--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC_Output.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC_Output.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\wings-testautomation\src\main\resources\menuItems\Sales\Transactions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE14BC9-30E6-4F4B-9913-01B069DE4218}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFD9765-DEF4-4223-93F2-05DFF13798AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="945" firstSheet="15" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="945" firstSheet="12" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
